--- a/sample_data/fixed_data/products_fixed.xlsx
+++ b/sample_data/fixed_data/products_fixed.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="修复后数据" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="__ecommerce_checker__" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,13 +414,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>SKU</t>
+          <t>商品编码</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -429,24 +430,338 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>错误信息</t>
+          <t>价格</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>库存</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>类目</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>店铺</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>主图</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>详情图</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>来源文件</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TEST001</t>
+          <t>PROD001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>假数据</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>这是模拟报告文件，不应被读取</t>
+          <t>无线蓝牙耳机高音质降噪运动耳机</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>199</v>
+      </c>
+      <c r="D2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>数码配件</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>旗舰店</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>images/PROD001_main.jpg</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>images/PROD001_detail_1.jpg;images/PROD001_detail_2.jpg;images/PROD001_detail_3.jpg</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>sample_data\products.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>PROD002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>这是一个超长标题这是一个超长标题这是一个超长标题这是一个超长标题这是一个超长标题这是一个超长标题这是一个超长标题这是一个</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>99.98999999999999</v>
+      </c>
+      <c r="D3" t="n">
+        <v>50</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>家居用品</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>专营店</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://cdn.example.com/images/PROD002.jpg</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>https://cdn.example.com/images/PROD002_detail_1.jpg;https://cdn.example.com/images/PROD002_detail_2.jpg</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>sample_data\products.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>PROD003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>高仿奢侈品包包原单复刻</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>999</v>
+      </c>
+      <c r="D4" t="n">
+        <v>20</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>箱包配饰</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>旗舰店</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>sample_data\products.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>PROD004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="n">
+        <v>50</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>服装</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>专营店</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>sample_data\products.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>PROD005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>纯棉T恤夏季新款短袖</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>-10</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-5</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>服装</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>旗舰店</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>sample_data\products.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PROD006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>运动鞋轻便透气跑步鞋</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>299</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-100</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>鞋靴</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>旗舰店</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>images/PROD001_main.jpg</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>images/PROD001_detail_1.jpg</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>sample_data\products.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>PROD007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>纯棉衬衫商务休闲长袖</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>159</v>
+      </c>
+      <c r="D8" t="n">
+        <v>30</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>服装</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>旗舰店</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://cdn.example.com/images/PROD007.jpg</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>sample_data\images\PROD007_detail_1.jpg;sample_data\images\PROD007_detail_2.jpg;sample_data\images\PROD007_detail_3.jpg</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>sample_data\products.xlsx</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>marker</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ecommerce_checker_tool_generated</t>
         </is>
       </c>
     </row>

--- a/sample_data/fixed_data/products_fixed.xlsx
+++ b/sample_data/fixed_data/products_fixed.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -515,7 +515,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>这是一个超长标题这是一个超长标题这是一个超长标题这是一个超长标题这是一个超长标题这是一个超长标题这是一个超长标题这是一个</t>
+          <t>这是一个超长标题这是一个超长标题这是一个超长标题这是一个超长标题这是一个超长标题这是一个超长标题这是</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -732,6 +732,127 @@
         </is>
       </c>
       <c r="I8" t="inlineStr">
+        <is>
+          <t>sample_data\products.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>PROD008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>小尺寸图片测试商品</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>89</v>
+      </c>
+      <c r="D9" t="n">
+        <v>50</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>家居用品</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>专营店</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>images/PROD008_main.jpg</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>images/PROD008_detail_1.jpg</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>sample_data\products.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>PROD009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>损坏图片测试商品</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>199</v>
+      </c>
+      <c r="D10" t="n">
+        <v>50</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>数码配件</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>专营店</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>images/PROD009_main.jpg</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>sample_data\products.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>PROD010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>大文件图片测试商品</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>299</v>
+      </c>
+      <c r="D11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>箱包配饰</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>专营店</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>images/PROD010_main.jpg</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
         <is>
           <t>sample_data\products.xlsx</t>
         </is>
